--- a/newspapers/Notifications_Log_Apr-Sep_2026.xlsx
+++ b/newspapers/Notifications_Log_Apr-Sep_2026.xlsx
@@ -729,7 +729,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>Compiled: 22 October 2026</t>
+          <t>Compiled: 22 October 2026; refreshed 29 October 2026</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="17" min="1" max="1"/>
@@ -3153,464 +3153,1824 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>SDEF India Scholarship Program 2026-27</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Swami Dayanand Education Foundation (SDEF)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Private / Foundation</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>First-year full-time professional UG students (2026-27) - B.Tech/BE, MBBS, BDS, B.Sc Nursing/B.Nursing, B.Pharm/Pharm.D, B.Arch and BVSc &amp; AH - at recognised Indian institutes; Class 12 &gt;= 80%; entrance cutoffs JEE Main AIR &lt;= 50,000, JEE Advanced AIR &lt;= 40,000, NEET UG AIR &lt;= 50,000, NATA &gt;= 100; no drop/gap year after Class 12</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>Annual family income &lt;= Rs 12 lakh</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>Annual; renewable up to 4 years subject to continued eligibility</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="17" t="inlineStr">
         <is>
           <t>Up to Rs 50,000 per year (Rs 20,000-Rs 50,000 by rank &amp; Class 10-12 average slab); up to Rs 2,00,000 over 4 years; 100-150 awards a year</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="17" t="inlineStr">
         <is>
           <t>Online only via the SDEF India Scholarship portal</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="17" t="inlineStr">
         <is>
           <t>Opened 15-Aug-2026; last date 31-Oct-2026 (results mid-Nov 2026; funding from Jan 2027)</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="17" t="inlineStr">
         <is>
           <t>https://www.swamidayanand.org/india-scholarships-2026-27</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="N29" s="17" t="inlineStr">
         <is>
           <t>swamidayanand.org; thehindu.com; news.aglasem.com</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="O29" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Aditya Birla Capital Scholarship Programme 2026-27 (girl students)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Aditya Birla Capital Foundation (via Buddy4Study)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Corporate / CSR</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>Meritorious girl students in Class 9-12, Polytechnic Diploma, UG or PG at recognised government schools/colleges/institutions across India; &gt;= 60% in the most recent academic year; children of Aditya Birla Capital / Buddy4Study employees not eligible</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>Girls only</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>Annual family income &lt;= Rs 6 lakh</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>One-time grant for one academic year</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>Rs 25,000 (Class 9-12 / Polytechnic Diploma); up to Rs 45,000 (UG); Rs 60,000 (PG)</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="17" t="inlineStr">
         <is>
           <t>Online via Buddy4Study</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="17" t="inlineStr">
         <is>
           <t>Opened 22-Sep-2026; last date 30-Oct-2026</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="17" t="inlineStr">
         <is>
           <t>https://www.buddy4study.com/page/aditya-birla-capital-scholarship</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="N30" s="17" t="inlineStr">
         <is>
           <t>buddy4study.com; educationtimes.com</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>ICAR Undergraduate National Talent Scholarship (NTS-UG) 2026</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Indian Council of Agricultural Research (ICAR) via NSP</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>Central - Govt</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>UG students in approved courses at Agricultural Universities, admitted outside their State of domicile; whole-time study with merit and good conduct</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>Not specified in the scheme notice</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>Annual; renewable subject to merit and good conduct</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr">
         <is>
           <t>Rs 3,000 per month</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>Online on NSP (OTR required)</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="17" t="inlineStr">
         <is>
           <t>31-Oct-2026</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="17" t="inlineStr">
         <is>
           <t>https://www.icar.org.in</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="N31" s="17" t="inlineStr">
         <is>
           <t>buddy4study.com; icar.org.in</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="O31" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>Labour Welfare Post-Matric Scholarship 2026-27 (Beedi/Cine/IOMC/LSDM workers' wards)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Ministry of Labour &amp; Employment (Labour Welfare Organisation) via NSP</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Central - Govt</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Children of Beedi, Cine, Iron Ore, Manganese Ore, Chrome Ore, Limestone &amp; Dolomite (LSDM) workers; Class 11 to PG/professional at recognised institutions; must have passed the previous qualifying exam on the first attempt</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>Beedi/cine workers' family income &lt;= Rs 10,000/month; mine workers per prescribed wage limits</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>Rs 3,000 (Class 11-12); Rs 6,000 (ITI/Polytechnic/UG); up to Rs 25,000 (professional - BE/MBBS/MBA)</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>Online on NSP (OTR required)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>31-Oct-2026 (institute verification 15-Nov-2026)</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="17" t="inlineStr">
         <is>
           <t>https://scholarships.gov.in</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="N32" s="17" t="inlineStr">
         <is>
           <t>timesofindia.indiatimes.com (10-Oct-2026)</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="O32" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Concentrix Scholarship Program 2026-27</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Concentrix Daksh Services India Pvt Ltd (with Buddy4Study India Foundation)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Corporate / CSR</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>Students across India - see the application page for the eligible education levels and income criteria</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>Not specified in the listing - confirm on the application page</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>Annual (per listing)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="17" t="inlineStr">
         <is>
           <t>Rs 65,000 (per listing)</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="17" t="inlineStr">
         <is>
           <t>Online via Buddy4Study</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>30-Oct-2026</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="17" t="inlineStr">
         <is>
           <t>https://www.buddy4study.com</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N33" s="17" t="inlineStr">
         <is>
           <t>indiascholarships.in (recently added, Oct 2026)</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Satya Scholarship Programme 2026-27</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>Satya Scholarship Programme (via Buddy4Study)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Private / Foundation</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>See the Buddy4Study listing for the eligible courses and income criteria</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>Not specified in the listing - confirm on the application page</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>Not specified</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>For the entire course duration (per listing)</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>100% of the annual course fee for the entire course duration, plus hostel/accommodation and meal support as per programme guidelines</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>Online via Buddy4Study</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t>31-Oct-2026</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="17" t="inlineStr">
         <is>
           <t>https://www.buddy4study.com</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N34" s="17" t="inlineStr">
         <is>
           <t>educationtimes.com (05-Oct-2026)</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PM USP Special Scholarship Scheme for Jammu &amp; Kashmir and Ladakh</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dept. of Higher Education, Ministry of Education (via NSP)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Students of J&amp;K and Ladakh domicile in UG/PG college and university courses</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Open to all (merit based)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Not specified in source</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Annual (renewable)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>See scheme page on NSP</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Opened 22-Oct-2026; student application till 31-Oct-2026 (institute verification 15-Nov-2026; L2 30-Nov-2026)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>National Scholarship for Post Graduate Studies (Merit Based)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ministry of Education (via NSP)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Students in PG / Masters programmes at recognised universities and colleges</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Open to all (merit based)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Not specified in source</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>See scheme page on NSP</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Opened 16-Sep-2026; student application till 31-Oct-2026 (institute verification 15-Nov-2026; L2 30-Nov-2026)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Prime Minister's Scholarship Scheme for Wards of States/UTs Police Personnel Martyred in Terror/Naxal Attacks</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs / Welfare and Rehabilitation Board (via NSP)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Wards/widows of police personnel martyred in terror or Naxal attacks - professional degree courses</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Open to all</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>All (separate rates for girls and boys)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Not specified in source</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Annual (renewable)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Monthly scholarship as per PMSS scheme rates - see NSP</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Prime Minister's Scholarship Scheme for Central Armed Police Forces (CAPF) and Assam Rifles</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ministry of Home Affairs / Welfare and Rehabilitation Board (via NSP)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Wards/widows of CAPF and Assam Rifles personnel - professional degree courses</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Open to all</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>All (separate rates for girls and boys)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Not specified in source</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Annual (renewable)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Monthly scholarship as per PMSS scheme rates - see NSP</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Prime Minister's Scholarship Scheme for Ministry of Railways</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ministry of Railways / Welfare and Rehabilitation Board (via NSP)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Wards/widows of Railway employees - professional degree courses</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Open to all</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>All (separate rates for girls and boys)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Not specified in source</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Annual (renewable)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Monthly scholarship as per PMSS scheme rates - see NSP</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>National Fellowship and Scholarship for Higher Education of ST Students (formerly Top Class Education for ST Students)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ministry of Tribal Affairs (via NSP)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ST students in specified institutions - UG, PG and research levels</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Scheduled Tribe (ST) only</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>As per Ministry of Tribal Affairs norms</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Full tuition/fee support plus living allowance as per scheme</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Central Sector Scholarship of Top Class Education for SC Students</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ministry of Social Justice and Empowerment (via NSP)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>SC students in notified top-class institutions - UG and PG</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Scheduled Caste (SC) only</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>As per Ministry of Social Justice norms</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Full tuition/fee support plus living allowance as per scheme</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Post-Matric Scholarship for Students with Disabilities</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities, Ministry of Social Justice (via NSP)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Students with 40% or more disability in Class 11 onward, UG, PG and professional courses</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Open to all (differently-abled)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>As per scheme norms</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Maintenance allowance plus book grant and fee support as per scheme</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Online on NSP after UDID consent; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Opened 25-Jul-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Scholarship for Top Class Education for Students with Disabilities</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Dept. of Empowerment of Persons with Disabilities, Ministry of Social Justice (via NSP)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Students with disability (40%+) in notified top-class institutions - UG and PG</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Open to all (differently-abled)</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>As per scheme norms</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Full tuition/fee support plus living allowance as per scheme</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Online on NSP after UDID consent; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ICAR Post Graduate Scholarship (PGS)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Indian Council of Agricultural Research (ICAR), Ministry of Agriculture (via NSP)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Students admitted to ICAR-recognised PG programmes in agriculture and allied sciences</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Open to all</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Annual (renewable)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Monthly scholarship as per ICAR norms</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ICAR National Talent Scholarship (NTS-PG)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Indian Council of Agricultural Research (ICAR) (via NSP)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Students admitted to PG programmes in agricultural universities outside their home state</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Open to all</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Annual (renewable)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Monthly scholarship as per ICAR norms</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ICAR Junior Research Fellowship (JRF) and Senior Research Fellowship (SRF)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Indian Council of Agricultural Research (ICAR) (via NSP)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Research students in agriculture and allied sciences at ICAR-recognised institutions</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Open to all</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>As per ICAR fellowship norms</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Annual (renewable)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Monthly fellowship as per ICAR norms</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>National Renewable Energy Fellowship Scheme</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ministry of New and Renewable Energy (via NSP)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Students pursuing PG / research in renewable energy and related disciplines</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Open to all (merit based)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Not specified in source</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Fellowship as per MNRE norms</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Stipend Scheme for UG and PG Studies at Indian Statistical Institute, Kolkata</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Indian Statistical Institute (ISI), Kolkata (via NSP)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Central - Institute</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Students admitted to ISI Kolkata UG and PG programmes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Open to all (merit based)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Not specified in source</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Monthly stipend as per ISI norms</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Opened 01-Jun-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Free Coaching for SCs, OBCs and beneficiaries of PM CARES for Children Scheme</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ministry of Social Justice and Empowerment (via NSP)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Candidates preparing for competitive / professional examinations - free coaching, not a cash award</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SC and OBC (plus PM CARES children)</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>As per scheme norms</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>As per scheme norms</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Free coaching support (no direct cash award)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Opened 03-Aug-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ishan Uday Special Scholarship Scheme for North Eastern Region (NER)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>University Grants Commission (UGC) (via NSP)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>NER-domicile students in the first year of UG degree/diploma courses</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Open to all (NER domicile)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>As per UGC norms</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Annual (renewable)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Monthly scholarship as per UGC norms</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Opened 16-Sep-2026; student application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>NEC Merit Scholarship - Financial Support to NER Students for Higher Professional Courses</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>North Eastern Council (NEC) (via NSP)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Central - Govt</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>NER-domicile students in higher professional courses</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Open to all (NER domicile)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>As per NEC norms</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Annual (renewal window)</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>As per NEC norms</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Online on NSP; Aadhaar OTR mandatory</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Renewal window opened 15-Jul-2026; application till 31-Oct-2026</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>https://scholarships.gov.in</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>scholarships.gov.in/All-Scholarships (checked 28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Open now - closes 31-Oct-2026</t>
         </is>
       </c>
     </row>
@@ -5959,268 +7319,268 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>LIC HFL Graduate Apprentice Recruitment 2026</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>LIC Housing Finance Ltd (LIC HFL)</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Banking / Financial Services (PSU)</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>Graduates (any discipline) for a 12-month paid apprenticeship; 232 posts</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>Open to all; reservation per rules</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>As per apprenticeship rules (see notification)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>Stipend as per the Apprentices Act (see notification)</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>12 months (Graduate Apprenticeship)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>Online via the LIC HFL / NATS portal</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>Last date 01-Nov-2026</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>https://www.lichousing.com</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t>thejobsme.com; sahisarkarijobs.in</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>IOCL Western Region Apprentice Recruitment 2026</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="17" t="inlineStr">
         <is>
           <t>Indian Oil Corporation Ltd (IOCL) - Western Region</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="17" t="inlineStr">
         <is>
           <t>Central PSU - Oil &amp; Gas</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="17" t="inlineStr">
         <is>
           <t>Trade, Technician and Graduate apprentices (ITI / Diploma / Graduate per trade); 335 posts</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="17" t="inlineStr">
         <is>
           <t>Open to all; reservation per rules</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="17" t="inlineStr">
         <is>
           <t>As per apprenticeship rules (see notification)</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="17" t="inlineStr">
         <is>
           <t>Stipend as per the Apprentices Act (see notification)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H35" s="17" t="inlineStr">
         <is>
           <t>Apprenticeship as per trade (typically 12-24 months)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" s="17" t="inlineStr">
         <is>
           <t>Online via the IOCL apprenticeship portal</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t>Last date 04-Nov-2026</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="17" t="inlineStr">
         <is>
           <t>https://www.iocl.com</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L35" s="17" t="inlineStr">
         <is>
           <t>hindustantimes.com; iocl.com</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="M35" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>NPCIL CA / CMA Internship 2026</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>Nuclear Power Corporation of India Ltd (NPCIL)</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="17" t="inlineStr">
         <is>
           <t>Central PSU - Nuclear Power</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>CA / CMA students for practical internship; 51 posts</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="17" t="inlineStr">
         <is>
           <t>Open to all</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>As per NPCIL internship norms (see notification)</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="17" t="inlineStr">
         <is>
           <t>Stipend as per NPCIL internship norms (see notification)</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H36" s="17" t="inlineStr">
         <is>
           <t>Internship as per ICAI / ICMAI norms</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" s="17" t="inlineStr">
         <is>
           <t>Online via the NPCIL portal</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="17" t="inlineStr">
         <is>
           <t>Last date 26-Oct-2026</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="17" t="inlineStr">
         <is>
           <t>https://www.npcil.nic.in</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" s="17" t="inlineStr">
         <is>
           <t>thejobsme.com</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="M36" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>DRDO Research Centre Imarat (RCI) Apprentice Recruitment 2026</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>DRDO - Research Centre Imarat (RCI), Hyderabad</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>Central Govt - Defence R&amp;D</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Graduate, Diploma and ITI apprentices; 195 vacancies</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>Open to all; reservation per rules</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="17" t="inlineStr">
         <is>
           <t>As per apprenticeship rules (see notification)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>Stipend as per the Apprentices Act (see notification)</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H37" s="17" t="inlineStr">
         <is>
           <t>Apprenticeship (typically 1 year)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" s="17" t="inlineStr">
         <is>
           <t>Online / offline per the DRDO advertisement</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="17" t="inlineStr">
         <is>
           <t>Per notification - late Oct to early Nov 2026 (listings differ; confirm on drdo.gov.in)</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="17" t="inlineStr">
         <is>
           <t>https://drdo.gov.in</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L37" s="17" t="inlineStr">
         <is>
           <t>hindustantimes.com; drdo.gov.in</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="M37" s="17" t="inlineStr">
         <is>
           <t>Open now</t>
         </is>
@@ -6240,7 +7600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="17" min="1" max="1"/>
@@ -8151,471 +9511,961 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>APPSC Group-I Services Recruitment 2026 (Notification 07/2026)</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>Andhra Pradesh Public Service Commission (APPSC)</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>AP State</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>166 posts (Group-I Services; provisional)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>Bachelor's degree (post-wise; see detailed notification)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Mostly 18-44 years as on 01-07-2026 (relaxations per AP rules)</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="17" t="inlineStr">
         <is>
           <t>AP communal roster; age relaxations for SC/ST/BC/PwD</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="17" t="inlineStr">
         <is>
           <t>Specific notification (2026)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" s="17" t="inlineStr">
         <is>
           <t>Apply online 06-Oct-2026 to 27-Oct-2026 (OTPR required)</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="17" t="inlineStr">
         <is>
           <t>See notification (schedule announced separately)</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="17" t="inlineStr">
         <is>
           <t>https://psc.ap.gov.in</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="L28" s="17" t="inlineStr">
         <is>
           <t>psc.ap.gov.in; prayasexam.in</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="M28" s="17" t="inlineStr">
         <is>
           <t>Open now - apply by 27-Oct-2026</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>APPSC Assistant Executive Engineer (AEE) Recruitment 2026</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="17" t="inlineStr">
         <is>
           <t>Andhra Pradesh Public Service Commission (APPSC)</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>AP State</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="17" t="inlineStr">
         <is>
           <t>503 Assistant Executive Engineer posts (provisional)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>BE/BTech/AMIE in the relevant engineering branch</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="17" t="inlineStr">
         <is>
           <t>18-44 years as on 01-07-2026 (relaxations per AP rules)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>AP communal roster applies</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="17" t="inlineStr">
         <is>
           <t>Specific notification (2026)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" s="17" t="inlineStr">
         <is>
           <t>Apply online; last date 22-Nov-2026 (see notification)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="17" t="inlineStr">
         <is>
           <t>See notification</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="17" t="inlineStr">
         <is>
           <t>https://psc.ap.gov.in</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="L29" s="17" t="inlineStr">
         <is>
           <t>psc.ap.gov.in; thejobsme.com; adda247.com</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="M29" s="17" t="inlineStr">
         <is>
           <t>Open now - apply by 22-Nov-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>APPSC Hostel Welfare Officer Grade-II Recruitment 2026 (Notification 25/2026)</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Andhra Pradesh Public Service Commission (APPSC)</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>AP State</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
         <is>
           <t>97 Hostel Welfare Officer Grade-II posts (Social, Tribal &amp; BC Welfare)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>Bachelor's degree (post-wise; see notification)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>18-44 years as on 01-07-2026 (relaxations per AP rules)</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="17" t="inlineStr">
         <is>
           <t>AP communal roster applies</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="17" t="inlineStr">
         <is>
           <t>Specific notification (2026)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" s="17" t="inlineStr">
         <is>
           <t>Apply online 09-Oct-2026 to 29-Oct-2026 (OTPR required)</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="17" t="inlineStr">
         <is>
           <t>See notification</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="17" t="inlineStr">
         <is>
           <t>https://psc.ap.gov.in</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="L30" s="17" t="inlineStr">
         <is>
           <t>psc.ap.gov.in; prayasexam.in</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="M30" s="17" t="inlineStr">
         <is>
           <t>Open now - apply by 29-Oct-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>AP DSC Teacher Recruitment 2026 (2,721 vacancies)</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>Department of School Education, Govt of Andhra Pradesh (AP DSC)</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="17" t="inlineStr">
         <is>
           <t>AP State</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="17" t="inlineStr">
         <is>
           <t>2,721 teacher vacancies (district-wise; provisional)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="17" t="inlineStr">
         <is>
           <t>As per NCTE / AP DSC norms (D.El.Ed / B.Ed with TET qualification)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="17" t="inlineStr">
         <is>
           <t>As per AP DSC rules (see notification)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="17" t="inlineStr">
         <is>
           <t>AP communal roster applies</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="17" t="inlineStr">
         <is>
           <t>Specific notification (2026)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" s="17" t="inlineStr">
         <is>
           <t>Notification dated 15-Oct-2026; application dates to be announced</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="17" t="inlineStr">
         <is>
           <t>CBT - dates to be announced</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="17" t="inlineStr">
         <is>
           <t>https://apdsc.apcfss.in</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L31" s="17" t="inlineStr">
         <is>
           <t>thejobsme.com; AP DSC notification</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M31" s="17" t="inlineStr">
         <is>
           <t>Upcoming - dates TBA</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="17" t="inlineStr">
         <is>
           <t>RRB NTPC (Graduate level) Recruitment 2026</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Railway Recruitment Boards (RRBs), Indian Railways</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="17" t="inlineStr">
         <is>
           <t>Central - Govt</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>3,548 Graduate-level NTPC posts (undergraduate-level NTPC notified separately with 1,688 posts)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="17" t="inlineStr">
         <is>
           <t>Bachelor's degree (Graduate level); 12th pass for the undergraduate level</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="17" t="inlineStr">
         <is>
           <t>18-33 years (relaxations per rules)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="17" t="inlineStr">
         <is>
           <t>Central govt reservation roster (SC/ST/OBC/EWS/PwBD)</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>Annual (CEN 2026)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>Notified 10-Oct-2026; last date 06-Nov-2026 (undergraduate level last date 13-Nov-2026)</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="17" t="inlineStr">
         <is>
           <t>CBT - schedule announced separately</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="17" t="inlineStr">
         <is>
           <t>https://indianrailways.gov.in</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="L32" s="17" t="inlineStr">
         <is>
           <t>rrbcdg.gov.in; thejobsme.com; adda247.com</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="M32" s="17" t="inlineStr">
         <is>
           <t>Open now - apply by 06-Nov-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>NICL Administrative Officer Recruitment 2026 (Scale I)</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>National Insurance Company Limited (NICL)</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="17" t="inlineStr">
         <is>
           <t>Central PSU</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="17" t="inlineStr">
         <is>
           <t>321 Administrative Officers (Generalists &amp; Specialists), Scale I</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="17" t="inlineStr">
         <is>
           <t>Graduation / Post-graduation (post-wise)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="17" t="inlineStr">
         <is>
           <t>21-30 years (relaxations per rules)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>Central PSU reservation roster</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H33" s="17" t="inlineStr">
         <is>
           <t>Specific recruitment (2026)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" s="17" t="inlineStr">
         <is>
           <t>Online registration 08-Oct-2026 to 28-Oct-2026</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="17" t="inlineStr">
         <is>
           <t>See notification</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="17" t="inlineStr">
         <is>
           <t>https://nationalinsurance.nic.co.in</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L33" s="17" t="inlineStr">
         <is>
           <t>ibpsreg.ibps.in; hindustantimes.com</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M33" s="17" t="inlineStr">
         <is>
           <t>Open now - apply by 28-Oct-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>ISRO SDSC SHAR Recruitment 2026 (Advertisement 03/2026)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="17" t="inlineStr">
         <is>
           <t>ISRO - Satish Dhawan Space Centre SHAR (Sriharikota, AP), Dept of Space</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="17" t="inlineStr">
         <is>
           <t>Central - Govt</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="17" t="inlineStr">
         <is>
           <t>97 posts - Technician-B, Technical Assistant, Draughtsman, Driver, MTS and others (provisional)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="17" t="inlineStr">
         <is>
           <t>ITI / Diploma / Degree in the relevant discipline (post-wise)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="17" t="inlineStr">
         <is>
           <t>18-35 years (post-wise; relaxations per rules)</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="17" t="inlineStr">
         <is>
           <t>Central govt roster incl. PwBD</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H34" s="17" t="inlineStr">
         <is>
           <t>Specific advertisement (03/2026 dated 19-Oct-2026)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" s="17" t="inlineStr">
         <is>
           <t>Online registration 19-Oct-2026 to 09-Nov-2026</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="17" t="inlineStr">
         <is>
           <t>Written / skill test - to be intimated separately</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="17" t="inlineStr">
         <is>
           <t>https://www.shar.gov.in</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L34" s="17" t="inlineStr">
         <is>
           <t>isro.gov.in (Advt 03/2026); shar.gov.in</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M34" s="17" t="inlineStr">
         <is>
           <t>Open now - apply by 09-Nov-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>APPSC Assistant Environmental Engineer 2026 (Notification No. 08/2026)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh Pollution Control Board via APPSC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AP State</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>41 posts (provisional)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>B.E./B.Tech in Environmental / Civil / Chemical engineering as specified</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>18-42 years (as on 01-07-2026)</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AP reservation roster applies</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Specific notification (08/2026, dated 06-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Apply online 06-Oct-2026 to 09-Nov-2026 (extended from 27-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>CBRT - date to be intimated</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>psc.ap.gov.in; thehindu.com (28-Oct-2026); edexlive.com (28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Open now - extended to 9-Nov-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>APPSC Horticulture Officer 2026 (Notification No. 19/2026)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>A.P. Horticulture Service via APPSC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AP State</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>37 posts (provisional)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>B.Sc (Agriculture) / Horticulture or equivalent as specified</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>18-42 years (as on 01-07-2026)</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>AP reservation roster applies</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Specific notification (19/2026, dated 06-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Apply online 06-Oct-2026 to 09-Nov-2026 (extended from 27-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>CBRT - date to be intimated</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>psc.ap.gov.in; thehindu.com (28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Open now - extended to 9-Nov-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>APPSC Assistant Social Welfare Officer / Assistant Tribal Welfare Officer 2026 (Notification No. 26/2026)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>A.P. Social Welfare Service and A.P. Tribal Welfare Service via APPSC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AP State</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>17 posts (provisional)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Degree with the subject combination specified in the notification</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>18-42 years (as on 01-07-2026)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>AP reservation roster applies</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Specific notification (26/2026, dated 09-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Apply online 09-Oct-2026 to 09-Nov-2026 (extended from 29-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>CBRT - date to be intimated</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>psc.ap.gov.in; edexlive.com (28-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Open now - extended to 9-Nov-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>APPSC Assistant Statistical Officer 2026 (Notification No. 20/2026)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>A.P. Economics and Statistical Subordinate Service via APPSC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AP State</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>196 posts (provisional)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Degree with Statistics / Mathematics / Economics as specified</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>18-42 years (as on 01-07-2026)</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>AP reservation roster applies</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Specific notification (20/2026, dated 13-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Apply online 13-Oct-2026 to 02-Nov-2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>CBRT - date to be intimated</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>psc.ap.gov.in; prayasexam.in (updated 17-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Open now - apply by 02-Nov-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>APPSC Supervisor Grade-I, Women Development and Child Welfare 2026 (Notification No. 13/2026) - women only</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>A.P. Women Development and Child Welfare Sub-Ordinate Service via APPSC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AP State</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29 posts (provisional; women candidates only)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Degree as specified in the notification</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>18-42 years (as on 01-07-2026)</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AP reservation roster applies; post reserved for women</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Specific notification (13/2026, dated 16-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Apply online 16-Oct-2026 to 05-Nov-2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>CBRT - date to be intimated</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>psc.ap.gov.in; prayasexam.in (updated 17-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Open now - apply by 05-Nov-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>APPSC Forest Range Officer / Forest Section Officer / Forest Beat Officer / Draughtsman Gr-II 2026 (Notifications 16, 17, 18 and 15/2026)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>A.P. Forest Service and A.P. Forest Subordinate Service via APPSC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AP State</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>73 posts (4 Forest Range Officer + 26 Forest Section Officer + 23 Forest Beat Officer + 20 Draughtsman Gr-II; provisional)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Degree (Forest Range Officer); Degree / Diploma as specified for subordinate posts</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>18-42 years (as on 01-07-2026)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>AP reservation roster applies</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Specific notifications dated 16-Oct-2026</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Apply online 16-Oct-2026 to 05-Nov-2026 (11:59 PM)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>CBRT - date to be intimated</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>psc.ap.gov.in; prayasexam.in (updated 17-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Open now - apply by 05-Nov-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>APPSC Group-II Services 2026 (Notification No. 37/2026) - 686 posts</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>APPSC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AP State</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>686 posts (provisional): Deputy Tahsildar 200, Deputy MPDO 176, Senior Accountant 90, Assistant Section Officer (GAD) 71, Junior Accountant 48, GST Officer 40, Prohibition &amp; Excise SI 29, Assistant Registrar of Cooperative Societies 10, Sub-Registrar 7, Municipal Commissioner Gr-III 6, ASO (Finance) 5, ASO (Law) 4</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bachelor's degree from a recognised university (post-specific subjects for accounts/legal posts)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>18-42 years (minimum 18; maximum 42 as reported)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>AP reservation roster applies</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Specific notification (brief notification 37/2026, dated 13-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Apply online 10-Nov-2026 to 30-Nov-2026 (11:59 PM); detailed notification on or before 10-Nov-2026</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Screening test (offline OMR) - date in detailed notification</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://psc.ap.gov.in</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>psc.ap.gov.in (Notification 37/2026 PDF); timesofindia.indiatimes.com (19-Oct-2026)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Upcoming - apply from 10-Nov-2026</t>
         </is>
       </c>
     </row>
